--- a/final_dataset.xlsx
+++ b/final_dataset.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E491"/>
+  <dimension ref="A1:E521"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13685,6 +13685,816 @@
         </is>
       </c>
     </row>
+    <row r="492">
+      <c r="A492" t="inlineStr">
+        <is>
+          <t>ಇನಿ ವಾರದ ವಾ ದಿನ</t>
+        </is>
+      </c>
+      <c r="B492" t="inlineStr">
+        <is>
+          <t>What day of the week is today</t>
+        </is>
+      </c>
+      <c r="C492" t="inlineStr">
+        <is>
+          <t>SYSTEM</t>
+        </is>
+      </c>
+      <c r="D492" t="inlineStr">
+        <is>
+          <t>day</t>
+        </is>
+      </c>
+      <c r="E492" t="inlineStr">
+        <is>
+          <t>date</t>
+        </is>
+      </c>
+    </row>
+    <row r="493">
+      <c r="A493" t="inlineStr">
+        <is>
+          <t>ಇನಿತ ಪೂರ್ತಿ ದಿನಾಂಕ ದಾದ</t>
+        </is>
+      </c>
+      <c r="B493" t="inlineStr">
+        <is>
+          <t>What is today’s full date</t>
+        </is>
+      </c>
+      <c r="C493" t="inlineStr">
+        <is>
+          <t>SYSTEM</t>
+        </is>
+      </c>
+      <c r="D493" t="inlineStr">
+        <is>
+          <t>date</t>
+        </is>
+      </c>
+      <c r="E493" t="inlineStr">
+        <is>
+          <t>date</t>
+        </is>
+      </c>
+    </row>
+    <row r="494">
+      <c r="A494" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ಕೋಡೆ ಒವ್ವು ದಿನ </t>
+        </is>
+      </c>
+      <c r="B494" t="inlineStr">
+        <is>
+          <t>What day was yesterday</t>
+        </is>
+      </c>
+      <c r="C494" t="inlineStr">
+        <is>
+          <t>SYSTEM</t>
+        </is>
+      </c>
+      <c r="D494" t="inlineStr">
+        <is>
+          <t>tomorrow_day</t>
+        </is>
+      </c>
+      <c r="E494" t="inlineStr">
+        <is>
+          <t>date</t>
+        </is>
+      </c>
+    </row>
+    <row r="495">
+      <c r="A495" t="inlineStr">
+        <is>
+          <t>ಎಲ್ಲೆ ದಾದ ದಿನ</t>
+        </is>
+      </c>
+      <c r="B495" t="inlineStr">
+        <is>
+          <t>What day is tomorrow</t>
+        </is>
+      </c>
+      <c r="C495" t="inlineStr">
+        <is>
+          <t>SYSTEM</t>
+        </is>
+      </c>
+      <c r="D495" t="inlineStr">
+        <is>
+          <t>yesterday_day</t>
+        </is>
+      </c>
+      <c r="E495" t="inlineStr">
+        <is>
+          <t>date</t>
+        </is>
+      </c>
+    </row>
+    <row r="496">
+      <c r="A496" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ಇನಿ ಒವ್ವು ದಿನ </t>
+        </is>
+      </c>
+      <c r="B496" t="inlineStr">
+        <is>
+          <t>What is the date now</t>
+        </is>
+      </c>
+      <c r="C496" t="inlineStr">
+        <is>
+          <t>SYSTEM</t>
+        </is>
+      </c>
+      <c r="D496" t="inlineStr">
+        <is>
+          <t>date</t>
+        </is>
+      </c>
+      <c r="E496" t="inlineStr">
+        <is>
+          <t>date</t>
+        </is>
+      </c>
+    </row>
+    <row r="497">
+      <c r="A497" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ಈ ತಿಂಗೊಲ್ದ ದಿನಾಂಕ ದಾದ </t>
+        </is>
+      </c>
+      <c r="B497" t="inlineStr">
+        <is>
+          <t>What is the date this month</t>
+        </is>
+      </c>
+      <c r="C497" t="inlineStr">
+        <is>
+          <t>SYSTEM</t>
+        </is>
+      </c>
+      <c r="D497" t="inlineStr">
+        <is>
+          <t>date</t>
+        </is>
+      </c>
+      <c r="E497" t="inlineStr">
+        <is>
+          <t>date</t>
+        </is>
+      </c>
+    </row>
+    <row r="498">
+      <c r="A498" t="inlineStr">
+        <is>
+          <t>ಇತ್ತೆ ವಾ ವರ್ಷ</t>
+        </is>
+      </c>
+      <c r="B498" t="inlineStr">
+        <is>
+          <t>Which year is now</t>
+        </is>
+      </c>
+      <c r="C498" t="inlineStr">
+        <is>
+          <t>SYSTEM</t>
+        </is>
+      </c>
+      <c r="D498" t="inlineStr">
+        <is>
+          <t>year</t>
+        </is>
+      </c>
+      <c r="E498" t="inlineStr">
+        <is>
+          <t>date</t>
+        </is>
+      </c>
+    </row>
+    <row r="499">
+      <c r="A499" t="inlineStr">
+        <is>
+          <t>ಒವ್ವು ತಿಂಗೊಲ್ ನಡತೊಂದುಂಡು</t>
+        </is>
+      </c>
+      <c r="B499" t="inlineStr">
+        <is>
+          <t>Which month is going on</t>
+        </is>
+      </c>
+      <c r="C499" t="inlineStr">
+        <is>
+          <t>SYSTEM</t>
+        </is>
+      </c>
+      <c r="D499" t="inlineStr">
+        <is>
+          <t>month</t>
+        </is>
+      </c>
+      <c r="E499" t="inlineStr">
+        <is>
+          <t>date</t>
+        </is>
+      </c>
+    </row>
+    <row r="500">
+      <c r="A500" t="inlineStr">
+        <is>
+          <t>ಇನಿತ  ದಿನ ಬೊಕ್ಕ ದಿನಾಂಕನ್ ಪನ್ಲೆ</t>
+        </is>
+      </c>
+      <c r="B500" t="inlineStr">
+        <is>
+          <t>Tell today’s day and date</t>
+        </is>
+      </c>
+      <c r="C500" t="inlineStr">
+        <is>
+          <t>SYSTEM</t>
+        </is>
+      </c>
+      <c r="D500" t="inlineStr">
+        <is>
+          <t>day_date</t>
+        </is>
+      </c>
+      <c r="E500" t="inlineStr">
+        <is>
+          <t>date</t>
+        </is>
+      </c>
+    </row>
+    <row r="501">
+      <c r="A501" t="inlineStr">
+        <is>
+          <t>ಇತ್ತೆ ಪೊರ್ತು ಬೊಕ್ಕ ದಿನಾಂಕ ದಾದ</t>
+        </is>
+      </c>
+      <c r="B501" t="inlineStr">
+        <is>
+          <t>What is the time and date now</t>
+        </is>
+      </c>
+      <c r="C501" t="inlineStr">
+        <is>
+          <t>SYSTEM</t>
+        </is>
+      </c>
+      <c r="D501" t="inlineStr">
+        <is>
+          <t>date_time</t>
+        </is>
+      </c>
+      <c r="E501" t="inlineStr">
+        <is>
+          <t>date</t>
+        </is>
+      </c>
+    </row>
+    <row r="502">
+      <c r="A502" t="inlineStr">
+        <is>
+          <t>ಗೇಟ್ ತೆರೆಲೆ</t>
+        </is>
+      </c>
+      <c r="B502" t="inlineStr">
+        <is>
+          <t>Open the gate</t>
+        </is>
+      </c>
+      <c r="C502" t="inlineStr">
+        <is>
+          <t>SYSTEM</t>
+        </is>
+      </c>
+      <c r="D502" t="inlineStr">
+        <is>
+          <t>open_gate</t>
+        </is>
+      </c>
+      <c r="E502" t="inlineStr">
+        <is>
+          <t>door_control</t>
+        </is>
+      </c>
+    </row>
+    <row r="503">
+      <c r="A503" t="inlineStr">
+        <is>
+          <t>ಗೇಟ್ ನ್ ಮುಚ್ಚುಲೆ</t>
+        </is>
+      </c>
+      <c r="B503" t="inlineStr">
+        <is>
+          <t>Close the gate</t>
+        </is>
+      </c>
+      <c r="C503" t="inlineStr">
+        <is>
+          <t>SYSTEM</t>
+        </is>
+      </c>
+      <c r="D503" t="inlineStr">
+        <is>
+          <t>close_gate</t>
+        </is>
+      </c>
+      <c r="E503" t="inlineStr">
+        <is>
+          <t>door_control</t>
+        </is>
+      </c>
+    </row>
+    <row r="504">
+      <c r="A504" t="inlineStr">
+        <is>
+          <t>ಕಿಟಕಿನ್ ತೆರೆಲೆ</t>
+        </is>
+      </c>
+      <c r="B504" t="inlineStr">
+        <is>
+          <t>Open the window</t>
+        </is>
+      </c>
+      <c r="C504" t="inlineStr">
+        <is>
+          <t>SYSTEM</t>
+        </is>
+      </c>
+      <c r="D504" t="inlineStr">
+        <is>
+          <t>open_window</t>
+        </is>
+      </c>
+      <c r="E504" t="inlineStr">
+        <is>
+          <t>door_control</t>
+        </is>
+      </c>
+    </row>
+    <row r="505">
+      <c r="A505" t="inlineStr">
+        <is>
+          <t>ಕಿಟಕಿನ್ ಮುಚ್ಚುಲೆ</t>
+        </is>
+      </c>
+      <c r="B505" t="inlineStr">
+        <is>
+          <t>Close the window</t>
+        </is>
+      </c>
+      <c r="C505" t="inlineStr">
+        <is>
+          <t>SYSTEM</t>
+        </is>
+      </c>
+      <c r="D505" t="inlineStr">
+        <is>
+          <t>close_window</t>
+        </is>
+      </c>
+      <c r="E505" t="inlineStr">
+        <is>
+          <t>door_control</t>
+        </is>
+      </c>
+    </row>
+    <row r="506">
+      <c r="A506" t="inlineStr">
+        <is>
+          <t>ಬಾಕಿಲ್ ಲಾಕ್ ಮಲ್ಪುಲೆ</t>
+        </is>
+      </c>
+      <c r="B506" t="inlineStr">
+        <is>
+          <t>Lock the door</t>
+        </is>
+      </c>
+      <c r="C506" t="inlineStr">
+        <is>
+          <t>SYSTEM</t>
+        </is>
+      </c>
+      <c r="D506" t="inlineStr">
+        <is>
+          <t>lock</t>
+        </is>
+      </c>
+      <c r="E506" t="inlineStr">
+        <is>
+          <t>door_control</t>
+        </is>
+      </c>
+    </row>
+    <row r="507">
+      <c r="A507" t="inlineStr">
+        <is>
+          <t>ಬಾಕಿಲ್ ತೆರೆಯೊಡು</t>
+        </is>
+      </c>
+      <c r="B507" t="inlineStr">
+        <is>
+          <t>Unlock the door</t>
+        </is>
+      </c>
+      <c r="C507" t="inlineStr">
+        <is>
+          <t>SYSTEM</t>
+        </is>
+      </c>
+      <c r="D507" t="inlineStr">
+        <is>
+          <t>unlock</t>
+        </is>
+      </c>
+      <c r="E507" t="inlineStr">
+        <is>
+          <t>door_control</t>
+        </is>
+      </c>
+    </row>
+    <row r="508">
+      <c r="A508" t="inlineStr">
+        <is>
+          <t>ಬಾಕಿಲ್ ನ್ ನೂಕುಲೆ</t>
+        </is>
+      </c>
+      <c r="B508" t="inlineStr">
+        <is>
+          <t>Push the door</t>
+        </is>
+      </c>
+      <c r="C508" t="inlineStr">
+        <is>
+          <t>SYSTEM</t>
+        </is>
+      </c>
+      <c r="D508" t="inlineStr">
+        <is>
+          <t>push</t>
+        </is>
+      </c>
+      <c r="E508" t="inlineStr">
+        <is>
+          <t>door_control</t>
+        </is>
+      </c>
+    </row>
+    <row r="509">
+      <c r="A509" t="inlineStr">
+        <is>
+          <t>ಬಾಕಿಲ್ ನ್ ಒಯಿಪುಲೆ</t>
+        </is>
+      </c>
+      <c r="B509" t="inlineStr">
+        <is>
+          <t>Pull the door</t>
+        </is>
+      </c>
+      <c r="C509" t="inlineStr">
+        <is>
+          <t>SYSTEM</t>
+        </is>
+      </c>
+      <c r="D509" t="inlineStr">
+        <is>
+          <t>pull</t>
+        </is>
+      </c>
+      <c r="E509" t="inlineStr">
+        <is>
+          <t>door_control</t>
+        </is>
+      </c>
+    </row>
+    <row r="510">
+      <c r="A510" t="inlineStr">
+        <is>
+          <t>ಪರದೆನ್ ತೆರೆಲೆ</t>
+        </is>
+      </c>
+      <c r="B510" t="inlineStr">
+        <is>
+          <t>Open the curtain</t>
+        </is>
+      </c>
+      <c r="C510" t="inlineStr">
+        <is>
+          <t>SYSTEM</t>
+        </is>
+      </c>
+      <c r="D510" t="inlineStr">
+        <is>
+          <t>open_curtain</t>
+        </is>
+      </c>
+      <c r="E510" t="inlineStr">
+        <is>
+          <t>door_control</t>
+        </is>
+      </c>
+    </row>
+    <row r="511">
+      <c r="A511" t="inlineStr">
+        <is>
+          <t>ಪರದೆನ್ ಮುಚ್ಚುಲೆ</t>
+        </is>
+      </c>
+      <c r="B511" t="inlineStr">
+        <is>
+          <t>Close the curtain</t>
+        </is>
+      </c>
+      <c r="C511" t="inlineStr">
+        <is>
+          <t>SYSTEM</t>
+        </is>
+      </c>
+      <c r="D511" t="inlineStr">
+        <is>
+          <t>close_curtain</t>
+        </is>
+      </c>
+      <c r="E511" t="inlineStr">
+        <is>
+          <t>door_control</t>
+        </is>
+      </c>
+    </row>
+    <row r="512">
+      <c r="A512" t="inlineStr">
+        <is>
+          <t>ಇಲ್ಲ್ ಪೊರ್ಲು ಉಂಡು</t>
+        </is>
+      </c>
+      <c r="B512" t="inlineStr">
+        <is>
+          <t>The house is beautiful</t>
+        </is>
+      </c>
+      <c r="C512" t="inlineStr">
+        <is>
+          <t>statement</t>
+        </is>
+      </c>
+      <c r="D512" t="inlineStr">
+        <is>
+          <t>description</t>
+        </is>
+      </c>
+      <c r="E512" t="inlineStr">
+        <is>
+          <t>description</t>
+        </is>
+      </c>
+    </row>
+    <row r="513">
+      <c r="A513" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ಈ ಸಾದಿ ಉದ್ದ ಉಂಡು </t>
+        </is>
+      </c>
+      <c r="B513" t="inlineStr">
+        <is>
+          <t>This road is long</t>
+        </is>
+      </c>
+      <c r="C513" t="inlineStr">
+        <is>
+          <t>statement</t>
+        </is>
+      </c>
+      <c r="D513" t="inlineStr">
+        <is>
+          <t>description</t>
+        </is>
+      </c>
+      <c r="E513" t="inlineStr">
+        <is>
+          <t>description</t>
+        </is>
+      </c>
+    </row>
+    <row r="514">
+      <c r="A514" t="inlineStr">
+        <is>
+          <t>ಈ  ಪರ್ನ್ದ್ ಚೀಪೆ ಉಂಡು</t>
+        </is>
+      </c>
+      <c r="B514" t="inlineStr">
+        <is>
+          <t>This fruit is sweet</t>
+        </is>
+      </c>
+      <c r="C514" t="inlineStr">
+        <is>
+          <t>statement</t>
+        </is>
+      </c>
+      <c r="D514" t="inlineStr">
+        <is>
+          <t>description</t>
+        </is>
+      </c>
+      <c r="E514" t="inlineStr">
+        <is>
+          <t>description</t>
+        </is>
+      </c>
+    </row>
+    <row r="515">
+      <c r="A515" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ಆ ಮರ ಉದ್ದ ಉಂಡು </t>
+        </is>
+      </c>
+      <c r="B515" t="inlineStr">
+        <is>
+          <t>That tree is tall</t>
+        </is>
+      </c>
+      <c r="C515" t="inlineStr">
+        <is>
+          <t>statement</t>
+        </is>
+      </c>
+      <c r="D515" t="inlineStr">
+        <is>
+          <t>description</t>
+        </is>
+      </c>
+      <c r="E515" t="inlineStr">
+        <is>
+          <t>description</t>
+        </is>
+      </c>
+    </row>
+    <row r="516">
+      <c r="A516" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ಈ ನೀರ್ ತಂಪು ಉಂಡು </t>
+        </is>
+      </c>
+      <c r="B516" t="inlineStr">
+        <is>
+          <t>This water is cold</t>
+        </is>
+      </c>
+      <c r="C516" t="inlineStr">
+        <is>
+          <t>statement</t>
+        </is>
+      </c>
+      <c r="D516" t="inlineStr">
+        <is>
+          <t>description</t>
+        </is>
+      </c>
+      <c r="E516" t="inlineStr">
+        <is>
+          <t>description</t>
+        </is>
+      </c>
+    </row>
+    <row r="517">
+      <c r="A517" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ಆ ಕೋಣೆ ಎಲ್ಯ ಉಂಡು </t>
+        </is>
+      </c>
+      <c r="B517" t="inlineStr">
+        <is>
+          <t>That room is small</t>
+        </is>
+      </c>
+      <c r="C517" t="inlineStr">
+        <is>
+          <t>statement</t>
+        </is>
+      </c>
+      <c r="D517" t="inlineStr">
+        <is>
+          <t>description</t>
+        </is>
+      </c>
+      <c r="E517" t="inlineStr">
+        <is>
+          <t>description</t>
+        </is>
+      </c>
+    </row>
+    <row r="518">
+      <c r="A518" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ಈ ಪುಸ್ತಕ ಕುತೂಹಲಕಾರಿ ಉಂಡು </t>
+        </is>
+      </c>
+      <c r="B518" t="inlineStr">
+        <is>
+          <t>This book is interesting</t>
+        </is>
+      </c>
+      <c r="C518" t="inlineStr">
+        <is>
+          <t>statement</t>
+        </is>
+      </c>
+      <c r="D518" t="inlineStr">
+        <is>
+          <t>description</t>
+        </is>
+      </c>
+      <c r="E518" t="inlineStr">
+        <is>
+          <t>description</t>
+        </is>
+      </c>
+    </row>
+    <row r="519">
+      <c r="A519" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ನಮ್ಮ ಊರುಡು ಶಾಂತಿಯುತವಾತ್ ಉಂಡು </t>
+        </is>
+      </c>
+      <c r="B519" t="inlineStr">
+        <is>
+          <t>Our village is peaceful</t>
+        </is>
+      </c>
+      <c r="C519" t="inlineStr">
+        <is>
+          <t>statement</t>
+        </is>
+      </c>
+      <c r="D519" t="inlineStr">
+        <is>
+          <t>description</t>
+        </is>
+      </c>
+      <c r="E519" t="inlineStr">
+        <is>
+          <t>description</t>
+        </is>
+      </c>
+    </row>
+    <row r="520">
+      <c r="A520" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ಈ ಪೂ ಪೊರ್ಲು ಉಂಡು </t>
+        </is>
+      </c>
+      <c r="B520" t="inlineStr">
+        <is>
+          <t>This flower is nice</t>
+        </is>
+      </c>
+      <c r="C520" t="inlineStr">
+        <is>
+          <t>statement</t>
+        </is>
+      </c>
+      <c r="D520" t="inlineStr">
+        <is>
+          <t>description</t>
+        </is>
+      </c>
+      <c r="E520" t="inlineStr">
+        <is>
+          <t>description</t>
+        </is>
+      </c>
+    </row>
+    <row r="521">
+      <c r="A521" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ಆ ಸುದೆ ಗುಂಡಿ ಉಂಡು </t>
+        </is>
+      </c>
+      <c r="B521" t="inlineStr">
+        <is>
+          <t>That river is deep</t>
+        </is>
+      </c>
+      <c r="C521" t="inlineStr">
+        <is>
+          <t>statement</t>
+        </is>
+      </c>
+      <c r="D521" t="inlineStr">
+        <is>
+          <t>description</t>
+        </is>
+      </c>
+      <c r="E521" t="inlineStr">
+        <is>
+          <t>description</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
